--- a/tracking/nexamart_m2_tracker.xlsx
+++ b/tracking/nexamart_m2_tracker.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>github.com/ARIF-rb/nexamart-m2 — working branch: master</t>
+          <t>github.com/ARIF-rb/nexamart-m2 — working branch: main</t>
         </is>
       </c>
     </row>
